--- a/Pyvanta_SQL_Questions_Import_Template.xlsx
+++ b/Pyvanta_SQL_Questions_Import_Template.xlsx
@@ -145,6 +145,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>OpenAI</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Student practice: keep StarterQuery/starterCode blank for an empty playground. Add the answer only in solution. The solution is hidden until the student selects View Solution; viewing it does not award learning points.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -590,6 +605,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/Pyvanta_SQL_Questions_Import_Template.xlsx
+++ b/Pyvanta_SQL_Questions_Import_Template.xlsx
@@ -145,21 +145,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Student practice: keep StarterQuery/starterCode blank for an empty playground. Add the answer only in solution. The solution is hidden until the student selects View Solution; viewing it does not award learning points.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -449,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -460,7 +445,7 @@
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="75" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -508,27 +493,32 @@
           <t>StarterQuery</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ReferenceSolution</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TimeLimit</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
@@ -576,21 +566,26 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SELECT column_name FROM table_name; -- instructor reference answer</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="2" t="b">
+      <c r="N2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -605,7 +600,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -615,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -677,6 +671,13 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ReferenceSolution contains the instructor answer. Keep StarterQuery blank so students start with an empty editor. Viewing the solution must not award learning points.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pyvanta_SQL_Questions_Import_Template.xlsx
+++ b/Pyvanta_SQL_Questions_Import_Template.xlsx
@@ -440,12 +440,12 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="75" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -527,7 +527,7 @@
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SQL-M6-001</t>
+          <t>SQL-SAMPLE-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Write a query to display the product name and price for products whose price is greater than 500. Sort the results by price from highest to lowest.</t>
+          <t>Return the name and price of products whose price is greater than 500. Sort by price from highest to lowest.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>A products table is created using the SchemaSQL column. It contains product records.</t>
+          <t>A products table is created using the SchemaSQL column.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -558,17 +558,13 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>CREATE TABLE products (product_id INTEGER PRIMARY KEY, name TEXT, price REAL, category TEXT);
-INSERT INTO products VALUES
-(1, 'Keyboard', 750, 'Accessories'),
-(2, 'Mouse', 350, 'Accessories'),
-(3, 'Monitor', 8500, 'Electronics'),
-(4, 'USB Cable', 200, 'Accessories');</t>
+INSERT INTO products VALUES (1, 'Keyboard', 750, 'Accessories'), (2, 'Mouse', 350, 'Accessories'), (3, 'Monitor', 8500, 'Electronics'), (4, 'USB Cable', 200, 'Accessories');</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SELECT column_name FROM table_name; -- instructor reference answer</t>
+          <t>SELECT name, price FROM products WHERE price &gt; 500 ORDER BY price DESC;</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
